--- a/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2857852-34B5-448D-AF4C-56779D8356EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936B43A0-931F-4915-A320-59066F388210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <t>com_taxnet</t>
   </si>
   <si>
-    <t>~TFM_UPD-TS</t>
+    <t>~TFM_UPD</t>
   </si>
 </sst>
 </file>

--- a/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936B43A0-931F-4915-A320-59066F388210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD68D627-15E3-4428-9E4B-9F7EBB8DFA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <t>com_taxnet</t>
   </si>
   <si>
-    <t>~TFM_UPD</t>
+    <t>~TFM_INS-TS</t>
   </si>
 </sst>
 </file>

--- a/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD68D627-15E3-4428-9E4B-9F7EBB8DFA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE63942A-84F0-4BC7-8B18-28256E34928E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Co2" sheetId="1" r:id="rId1"/>
+    <sheet name="fuel_costs" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>commodity</t>
   </si>
@@ -57,12 +58,33 @@
   </si>
   <si>
     <t>~TFM_INS-TS</t>
+  </si>
+  <si>
+    <t>~TFM_INS-TS: attribute=flo_cost</t>
+  </si>
+  <si>
+    <t>pset_co</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Coal</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Bioenergy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -92,8 +114,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,4 +474,185 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13560296-7955-4D55-8E7E-094E43148A2D}">
+  <dimension ref="A2:I7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>2022</v>
+      </c>
+      <c r="D3">
+        <v>2025</v>
+      </c>
+      <c r="E3">
+        <v>2030</v>
+      </c>
+      <c r="F3">
+        <v>2035</v>
+      </c>
+      <c r="G3">
+        <v>2040</v>
+      </c>
+      <c r="H3">
+        <v>2045</v>
+      </c>
+      <c r="I3">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1">
+        <v>35.145058821884028</v>
+      </c>
+      <c r="D4" s="1">
+        <v>35.145058821884028</v>
+      </c>
+      <c r="E4" s="1">
+        <v>34.442157645446351</v>
+      </c>
+      <c r="F4" s="1">
+        <v>33.75331449253742</v>
+      </c>
+      <c r="G4" s="1">
+        <f>F4+F4*0.03</f>
+        <v>34.765913927313541</v>
+      </c>
+      <c r="H4" s="1">
+        <f>G4+G4*0.03</f>
+        <v>35.808891345132949</v>
+      </c>
+      <c r="I4" s="1">
+        <f>H4+H4*0.03</f>
+        <v>36.88315808548694</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>96.367112810707454</v>
+      </c>
+      <c r="D5" s="1">
+        <v>96.367112810707454</v>
+      </c>
+      <c r="E5" s="1">
+        <f>D5+(D5*0.03)</f>
+        <v>99.25812619502868</v>
+      </c>
+      <c r="F5" s="1">
+        <f>E5+(E5*0.03)</f>
+        <v>102.23586998087954</v>
+      </c>
+      <c r="G5" s="1">
+        <f>F5+(F5*0.03)</f>
+        <v>105.30294608030593</v>
+      </c>
+      <c r="H5" s="1">
+        <f>G5+(G5*0.03)</f>
+        <v>108.46203446271511</v>
+      </c>
+      <c r="I5" s="1">
+        <f>H5+(H5*0.03)</f>
+        <v>111.71589549659656</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46.470588235294123</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46.470588235294123</v>
+      </c>
+      <c r="E6" s="1">
+        <f>D6+(D6*0.03)</f>
+        <v>47.864705882352943</v>
+      </c>
+      <c r="F6" s="1">
+        <f>E6+(E6*0.03)</f>
+        <v>49.300647058823529</v>
+      </c>
+      <c r="G6" s="1">
+        <f>F6+(F6*0.03)</f>
+        <v>50.779666470588232</v>
+      </c>
+      <c r="H6" s="1">
+        <f>G6+(G6*0.03)</f>
+        <v>52.303056464705882</v>
+      </c>
+      <c r="I6" s="1">
+        <f>H6+(H6*0.03)</f>
+        <v>53.872148158647057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45.792000000000002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>45.792000000000002</v>
+      </c>
+      <c r="E7" s="1">
+        <f>D7-(D7*0.02)</f>
+        <v>44.876159999999999</v>
+      </c>
+      <c r="F7" s="1">
+        <f>E7-(E7*0.02)</f>
+        <v>43.978636799999997</v>
+      </c>
+      <c r="G7" s="1">
+        <f>F7-(F7*0.02)</f>
+        <v>43.099064063999997</v>
+      </c>
+      <c r="H7" s="1">
+        <f>G7-(G7*0.02)</f>
+        <v>42.237082782719995</v>
+      </c>
+      <c r="I7" s="1">
+        <f>H7+(H7*0.02)</f>
+        <v>43.081824438374397</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE63942A-84F0-4BC7-8B18-28256E34928E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C909134C-35B3-4AB6-AC34-051AD30D5DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Co2" sheetId="1" r:id="rId1"/>
@@ -478,7 +478,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13560296-7955-4D55-8E7E-094E43148A2D}">
-  <dimension ref="A2:I7"/>
+  <dimension ref="A2:I10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" bestFit="1" customWidth="1"/>
@@ -557,30 +557,30 @@
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1">
-        <v>96.367112810707454</v>
-      </c>
-      <c r="D5" s="1">
-        <v>96.367112810707454</v>
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
       </c>
       <c r="E5" s="1">
-        <f>D5+(D5*0.03)</f>
+        <f>D10+(D10*0.03)</f>
         <v>99.25812619502868</v>
       </c>
       <c r="F5" s="1">
-        <f>E5+(E5*0.03)</f>
+        <f t="shared" ref="E5:I6" si="0">E5+(E5*0.03)</f>
         <v>102.23586998087954</v>
       </c>
       <c r="G5" s="1">
-        <f>F5+(F5*0.03)</f>
+        <f t="shared" si="0"/>
         <v>105.30294608030593</v>
       </c>
       <c r="H5" s="1">
-        <f>G5+(G5*0.03)</f>
+        <f t="shared" si="0"/>
         <v>108.46203446271511</v>
       </c>
       <c r="I5" s="1">
-        <f>H5+(H5*0.03)</f>
+        <f t="shared" si="0"/>
         <v>111.71589549659656</v>
       </c>
     </row>
@@ -598,23 +598,23 @@
         <v>46.470588235294123</v>
       </c>
       <c r="E6" s="1">
-        <f>D6+(D6*0.03)</f>
+        <f t="shared" si="0"/>
         <v>47.864705882352943</v>
       </c>
       <c r="F6" s="1">
-        <f>E6+(E6*0.03)</f>
+        <f t="shared" si="0"/>
         <v>49.300647058823529</v>
       </c>
       <c r="G6" s="1">
-        <f>F6+(F6*0.03)</f>
+        <f t="shared" si="0"/>
         <v>50.779666470588232</v>
       </c>
       <c r="H6" s="1">
-        <f>G6+(G6*0.03)</f>
+        <f t="shared" si="0"/>
         <v>52.303056464705882</v>
       </c>
       <c r="I6" s="1">
-        <f>H6+(H6*0.03)</f>
+        <f t="shared" si="0"/>
         <v>53.872148158647057</v>
       </c>
     </row>
@@ -650,6 +650,14 @@
       <c r="I7" s="1">
         <f>H7+(H7*0.02)</f>
         <v>43.081824438374397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C10" s="1">
+        <v>96.367112810707454</v>
+      </c>
+      <c r="D10" s="1">
+        <v>96.367112810707454</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C909134C-35B3-4AB6-AC34-051AD30D5DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F21EE9-7F98-42CE-9494-3DA751702A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Co2" sheetId="1" r:id="rId1"/>
@@ -398,14 +398,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A4:I7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -434,7 +434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -442,30 +442,30 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7">
-        <v>8.6999999999999994E-2</v>
+        <v>7.2599999999999998E-2</v>
       </c>
       <c r="C7">
-        <v>8.6999999999999994E-2</v>
+        <v>7.2599999999999998E-2</v>
       </c>
       <c r="D7">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="E7">
+        <v>0.125</v>
+      </c>
+      <c r="F7">
+        <v>0.16</v>
+      </c>
+      <c r="G7">
         <v>0.18</v>
       </c>
-      <c r="F7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G7">
-        <v>0.23</v>
-      </c>
       <c r="H7">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I7" t="s">
         <v>5</v>
@@ -479,17 +479,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13560296-7955-4D55-8E7E-094E43148A2D}">
   <dimension ref="A2:I10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -518,7 +518,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -535,56 +535,52 @@
         <v>34.442157645446351</v>
       </c>
       <c r="F4" s="1">
-        <v>33.75331449253742</v>
+        <v>14.330994859409021</v>
       </c>
       <c r="G4" s="1">
-        <f>F4+F4*0.03</f>
-        <v>34.765913927313541</v>
+        <f>F4-F4*0.03</f>
+        <v>13.90106501362675</v>
       </c>
       <c r="H4" s="1">
-        <f>G4+G4*0.03</f>
-        <v>35.808891345132949</v>
+        <f>G4-G4*0.03</f>
+        <v>13.484033063217948</v>
       </c>
       <c r="I4" s="1">
-        <f>H4+H4*0.03</f>
-        <v>36.88315808548694</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+        <v>13.648566532770493</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5">
-        <v>60</v>
-      </c>
-      <c r="D5">
-        <v>60</v>
+      <c r="C5" s="1">
+        <v>96.367112810707454</v>
+      </c>
+      <c r="D5" s="1">
+        <v>96.367112810707454</v>
       </c>
       <c r="E5" s="1">
-        <f>D10+(D10*0.03)</f>
-        <v>99.25812619502868</v>
+        <v>64</v>
       </c>
       <c r="F5" s="1">
-        <f t="shared" ref="E5:I6" si="0">E5+(E5*0.03)</f>
-        <v>102.23586998087954</v>
+        <v>40.439770554493307</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="0"/>
-        <v>105.30294608030593</v>
+        <f>F5-(F5*0.05)</f>
+        <v>38.417782026768641</v>
       </c>
       <c r="H5" s="1">
-        <f t="shared" si="0"/>
-        <v>108.46203446271511</v>
+        <f>G5-(G5*0.05)</f>
+        <v>36.49689292543021</v>
       </c>
       <c r="I5" s="1">
-        <f t="shared" si="0"/>
-        <v>111.71589549659656</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+        <v>33.556405353728486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -598,27 +594,22 @@
         <v>46.470588235294123</v>
       </c>
       <c r="E6" s="1">
-        <f t="shared" si="0"/>
-        <v>47.864705882352943</v>
+        <v>35</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" si="0"/>
-        <v>49.300647058823529</v>
+        <v>28.393881453154876</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="0"/>
-        <v>50.779666470588232</v>
+        <v>25</v>
       </c>
       <c r="H6" s="1">
-        <f t="shared" si="0"/>
-        <v>52.303056464705882</v>
+        <v>23</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" si="0"/>
-        <v>53.872148158647057</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+        <v>21.510516252390055</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -652,7 +643,7 @@
         <v>43.081824438374397</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C10" s="1">
         <v>96.367112810707454</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F21EE9-7F98-42CE-9494-3DA751702A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969A6C3C-937B-4A71-9814-98F1272C2C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Co2" sheetId="1" r:id="rId1"/>
@@ -397,44 +397,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:I7"/>
+  <dimension ref="A4:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
       <c r="B5">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="C5">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="D5">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="E5">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="F5">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="G5">
-        <v>2045</v>
-      </c>
-      <c r="H5">
         <v>2050</v>
       </c>
-      <c r="I5" t="s">
+      <c r="H5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -442,7 +439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -450,24 +447,21 @@
         <v>7.2599999999999998E-2</v>
       </c>
       <c r="C7">
-        <v>7.2599999999999998E-2</v>
+        <v>0.1</v>
       </c>
       <c r="D7">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="E7">
-        <v>0.125</v>
+        <v>0.16</v>
       </c>
       <c r="F7">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="G7">
-        <v>0.18</v>
-      </c>
-      <c r="H7">
         <v>0.2</v>
       </c>
-      <c r="I7" t="s">
+      <c r="H7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -478,18 +472,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13560296-7955-4D55-8E7E-094E43148A2D}">
-  <dimension ref="A2:I10"/>
+  <dimension ref="A2:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -497,28 +491,25 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D3">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="E3">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="F3">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="G3">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="H3">
-        <v>2045</v>
-      </c>
-      <c r="I3">
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -529,27 +520,24 @@
         <v>35.145058821884028</v>
       </c>
       <c r="D4" s="1">
-        <v>35.145058821884028</v>
+        <v>34.442157645446351</v>
       </c>
       <c r="E4" s="1">
-        <v>34.442157645446351</v>
+        <v>14.330994859409021</v>
       </c>
       <c r="F4" s="1">
-        <v>14.330994859409021</v>
+        <f>E4-E4*0.03</f>
+        <v>13.90106501362675</v>
       </c>
       <c r="G4" s="1">
         <f>F4-F4*0.03</f>
-        <v>13.90106501362675</v>
+        <v>13.484033063217948</v>
       </c>
       <c r="H4" s="1">
-        <f>G4-G4*0.03</f>
-        <v>13.484033063217948</v>
-      </c>
-      <c r="I4" s="1">
         <v>13.648566532770493</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -560,27 +548,24 @@
         <v>96.367112810707454</v>
       </c>
       <c r="D5" s="1">
-        <v>96.367112810707454</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1">
-        <v>64</v>
+        <v>40.439770554493307</v>
       </c>
       <c r="F5" s="1">
-        <v>40.439770554493307</v>
+        <f>E5-(E5*0.05)</f>
+        <v>38.417782026768641</v>
       </c>
       <c r="G5" s="1">
         <f>F5-(F5*0.05)</f>
-        <v>38.417782026768641</v>
+        <v>36.49689292543021</v>
       </c>
       <c r="H5" s="1">
-        <f>G5-(G5*0.05)</f>
-        <v>36.49689292543021</v>
-      </c>
-      <c r="I5" s="1">
         <v>33.556405353728486</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -591,25 +576,22 @@
         <v>46.470588235294123</v>
       </c>
       <c r="D6" s="1">
-        <v>46.470588235294123</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1">
-        <v>35</v>
+        <v>28.393881453154876</v>
       </c>
       <c r="F6" s="1">
-        <v>28.393881453154876</v>
+        <v>25</v>
       </c>
       <c r="G6" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H6" s="1">
-        <v>23</v>
-      </c>
-      <c r="I6" s="1">
         <v>21.510516252390055</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -620,30 +602,27 @@
         <v>45.792000000000002</v>
       </c>
       <c r="D7" s="1">
-        <v>45.792000000000002</v>
+        <f>C7-(C7*0.02)</f>
+        <v>44.876159999999999</v>
       </c>
       <c r="E7" s="1">
         <f>D7-(D7*0.02)</f>
-        <v>44.876159999999999</v>
+        <v>43.978636799999997</v>
       </c>
       <c r="F7" s="1">
         <f>E7-(E7*0.02)</f>
-        <v>43.978636799999997</v>
+        <v>43.099064063999997</v>
       </c>
       <c r="G7" s="1">
         <f>F7-(F7*0.02)</f>
-        <v>43.099064063999997</v>
+        <v>42.237082782719995</v>
       </c>
       <c r="H7" s="1">
-        <f>G7-(G7*0.02)</f>
-        <v>42.237082782719995</v>
-      </c>
-      <c r="I7" s="1">
-        <f>H7+(H7*0.02)</f>
+        <f>G7+(G7*0.02)</f>
         <v>43.081824438374397</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C10" s="1">
         <v>96.367112810707454</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969A6C3C-937B-4A71-9814-98F1272C2C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC540476-44D6-4165-A723-DDE115F33E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Co2" sheetId="1" r:id="rId1"/>
@@ -447,19 +447,19 @@
         <v>7.2599999999999998E-2</v>
       </c>
       <c r="C7">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D7">
-        <v>0.125</v>
+        <v>0.18</v>
       </c>
       <c r="E7">
-        <v>0.16</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="F7">
-        <v>0.18</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="G7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H7" t="s">
         <v>5</v>

--- a/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC540476-44D6-4165-A723-DDE115F33E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC3D9DF-9A70-4B4B-A9F0-BFD9F833C5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Co2" sheetId="1" r:id="rId1"/>
@@ -397,41 +397,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:H7"/>
+  <dimension ref="A4:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
       <c r="B5">
+        <v>2022</v>
+      </c>
+      <c r="C5">
         <v>2025</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>2030</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>2035</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>2040</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>2045</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>2050</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -439,29 +442,32 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7">
+        <v>0.08</v>
+      </c>
+      <c r="C7">
         <v>7.2599999999999998E-2</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.15</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.18</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.20499999999999999</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.23499999999999999</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.25</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -472,18 +478,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13560296-7955-4D55-8E7E-094E43148A2D}">
-  <dimension ref="A2:H10"/>
+  <dimension ref="A2:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -491,25 +498,28 @@
         <v>8</v>
       </c>
       <c r="C3">
+        <v>2022</v>
+      </c>
+      <c r="D3">
         <v>2025</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>2030</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>2035</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>2040</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>2045</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -517,27 +527,31 @@
         <v>9</v>
       </c>
       <c r="C4" s="1">
+        <f>D4*(1+0.01)</f>
+        <v>35.496509410102867</v>
+      </c>
+      <c r="D4" s="1">
         <v>35.145058821884028</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>34.442157645446351</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>14.330994859409021</v>
-      </c>
-      <c r="F4" s="1">
-        <f>E4-E4*0.03</f>
-        <v>13.90106501362675</v>
       </c>
       <c r="G4" s="1">
         <f>F4-F4*0.03</f>
+        <v>13.90106501362675</v>
+      </c>
+      <c r="H4" s="1">
+        <f>G4-G4*0.03</f>
         <v>13.484033063217948</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>13.648566532770493</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -545,27 +559,31 @@
         <v>10</v>
       </c>
       <c r="C5" s="1">
+        <f t="shared" ref="C5:C7" si="0">D5*(1+0.01)</f>
+        <v>97.330783938814534</v>
+      </c>
+      <c r="D5" s="1">
         <v>96.367112810707454</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>64</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>40.439770554493307</v>
-      </c>
-      <c r="F5" s="1">
-        <f>E5-(E5*0.05)</f>
-        <v>38.417782026768641</v>
       </c>
       <c r="G5" s="1">
         <f>F5-(F5*0.05)</f>
+        <v>38.417782026768641</v>
+      </c>
+      <c r="H5" s="1">
+        <f>G5-(G5*0.05)</f>
         <v>36.49689292543021</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>33.556405353728486</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -573,25 +591,29 @@
         <v>11</v>
       </c>
       <c r="C6" s="1">
+        <f t="shared" si="0"/>
+        <v>46.935294117647068</v>
+      </c>
+      <c r="D6" s="1">
         <v>46.470588235294123</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>35</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>28.393881453154876</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>25</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>23</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>21.510516252390055</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -599,30 +621,34 @@
         <v>12</v>
       </c>
       <c r="C7" s="1">
+        <f t="shared" si="0"/>
+        <v>46.249920000000003</v>
+      </c>
+      <c r="D7" s="1">
         <v>45.792000000000002</v>
-      </c>
-      <c r="D7" s="1">
-        <f>C7-(C7*0.02)</f>
-        <v>44.876159999999999</v>
       </c>
       <c r="E7" s="1">
         <f>D7-(D7*0.02)</f>
-        <v>43.978636799999997</v>
+        <v>44.876159999999999</v>
       </c>
       <c r="F7" s="1">
         <f>E7-(E7*0.02)</f>
-        <v>43.099064063999997</v>
+        <v>43.978636799999997</v>
       </c>
       <c r="G7" s="1">
         <f>F7-(F7*0.02)</f>
+        <v>43.099064063999997</v>
+      </c>
+      <c r="H7" s="1">
+        <f>G7-(G7*0.02)</f>
         <v>42.237082782719995</v>
       </c>
-      <c r="H7" s="1">
-        <f>G7+(G7*0.02)</f>
+      <c r="I7" s="1">
+        <f>H7+(H7*0.02)</f>
         <v>43.081824438374397</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C10" s="1">
         <v>96.367112810707454</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_base2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC3D9DF-9A70-4B4B-A9F0-BFD9F833C5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5008272B-93D8-4A79-8CED-29B9E58F6C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Co2" sheetId="1" r:id="rId1"/>
@@ -37,13 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
-  <si>
-    <t>commodity</t>
-  </si>
-  <si>
-    <t>attribute</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
   <si>
     <t>*</t>
   </si>
@@ -60,9 +54,6 @@
     <t>~TFM_INS-TS</t>
   </si>
   <si>
-    <t>~TFM_INS-TS: attribute=flo_cost</t>
-  </si>
-  <si>
     <t>pset_co</t>
   </si>
   <si>
@@ -76,6 +67,21 @@
   </si>
   <si>
     <t>Bioenergy</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Commodity</t>
+  </si>
+  <si>
+    <t>flo_cost</t>
   </si>
 </sst>
 </file>
@@ -85,7 +91,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,16 +99,53 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -110,16 +153,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{E7721F1E-C9FA-44D3-ACD5-45203FA64607}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -397,78 +458,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:I7"/>
+  <dimension ref="B6:L9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2022</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2025</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2030</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2035</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2040</v>
+      </c>
+      <c r="J7" s="5">
+        <v>2045</v>
+      </c>
+      <c r="K7" s="5">
+        <v>2050</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5">
-        <v>2022</v>
-      </c>
-      <c r="C5">
-        <v>2025</v>
-      </c>
-      <c r="D5">
-        <v>2030</v>
-      </c>
-      <c r="E5">
-        <v>2035</v>
-      </c>
-      <c r="F5">
-        <v>2040</v>
-      </c>
-      <c r="G5">
-        <v>2045</v>
-      </c>
-      <c r="H5">
-        <v>2050</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="C8" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>0.08</v>
+      </c>
+      <c r="F9">
+        <v>7.2599999999999998E-2</v>
+      </c>
+      <c r="G9">
+        <v>0.15</v>
+      </c>
+      <c r="H9">
+        <v>0.18</v>
+      </c>
+      <c r="I9">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="J9">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="K9">
+        <v>0.25</v>
+      </c>
+      <c r="L9" t="s">
         <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>0.08</v>
-      </c>
-      <c r="C7">
-        <v>7.2599999999999998E-2</v>
-      </c>
-      <c r="D7">
-        <v>0.15</v>
-      </c>
-      <c r="E7">
-        <v>0.18</v>
-      </c>
-      <c r="F7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G7">
-        <v>0.23499999999999999</v>
-      </c>
-      <c r="H7">
-        <v>0.25</v>
-      </c>
-      <c r="I7" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -478,183 +553,208 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13560296-7955-4D55-8E7E-094E43148A2D}">
-  <dimension ref="A2:I10"/>
+  <dimension ref="B3:M10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2022</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2030</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2035</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2040</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2045</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2050</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1">
+        <f>G5*(1+0.01)</f>
+        <v>35.496509410102867</v>
+      </c>
+      <c r="G5" s="1">
+        <v>35.145058821884028</v>
+      </c>
+      <c r="H5" s="1">
+        <v>34.442157645446351</v>
+      </c>
+      <c r="I5" s="1">
+        <v>14.330994859409021</v>
+      </c>
+      <c r="J5" s="1">
+        <f>I5-I5*0.03</f>
+        <v>13.90106501362675</v>
+      </c>
+      <c r="K5" s="1">
+        <f>J5-J5*0.03</f>
+        <v>13.484033063217948</v>
+      </c>
+      <c r="L5" s="1">
+        <v>13.648566532770493</v>
+      </c>
+      <c r="M5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" ref="F6:F8" si="0">G6*(1+0.01)</f>
+        <v>97.330783938814534</v>
+      </c>
+      <c r="G6" s="1">
+        <v>96.367112810707454</v>
+      </c>
+      <c r="H6" s="1">
+        <v>64</v>
+      </c>
+      <c r="I6" s="1">
+        <v>40.439770554493307</v>
+      </c>
+      <c r="J6" s="1">
+        <f>I6-(I6*0.05)</f>
+        <v>38.417782026768641</v>
+      </c>
+      <c r="K6" s="1">
+        <f>J6-(J6*0.05)</f>
+        <v>36.49689292543021</v>
+      </c>
+      <c r="L6" s="1">
+        <v>33.556405353728486</v>
+      </c>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
         <v>8</v>
       </c>
-      <c r="C3">
-        <v>2022</v>
-      </c>
-      <c r="D3">
-        <v>2025</v>
-      </c>
-      <c r="E3">
-        <v>2030</v>
-      </c>
-      <c r="F3">
-        <v>2035</v>
-      </c>
-      <c r="G3">
-        <v>2040</v>
-      </c>
-      <c r="H3">
-        <v>2045</v>
-      </c>
-      <c r="I3">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1">
-        <f>D4*(1+0.01)</f>
-        <v>35.496509410102867</v>
-      </c>
-      <c r="D4" s="1">
-        <v>35.145058821884028</v>
-      </c>
-      <c r="E4" s="1">
-        <v>34.442157645446351</v>
-      </c>
-      <c r="F4" s="1">
-        <v>14.330994859409021</v>
-      </c>
-      <c r="G4" s="1">
-        <f>F4-F4*0.03</f>
-        <v>13.90106501362675</v>
-      </c>
-      <c r="H4" s="1">
-        <f>G4-G4*0.03</f>
-        <v>13.484033063217948</v>
-      </c>
-      <c r="I4" s="1">
-        <v>13.648566532770493</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1">
-        <f t="shared" ref="C5:C7" si="0">D5*(1+0.01)</f>
-        <v>97.330783938814534</v>
-      </c>
-      <c r="D5" s="1">
-        <v>96.367112810707454</v>
-      </c>
-      <c r="E5" s="1">
-        <v>64</v>
-      </c>
-      <c r="F5" s="1">
-        <v>40.439770554493307</v>
-      </c>
-      <c r="G5" s="1">
-        <f>F5-(F5*0.05)</f>
-        <v>38.417782026768641</v>
-      </c>
-      <c r="H5" s="1">
-        <f>G5-(G5*0.05)</f>
-        <v>36.49689292543021</v>
-      </c>
-      <c r="I5" s="1">
-        <v>33.556405353728486</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1">
         <f t="shared" si="0"/>
         <v>46.935294117647068</v>
       </c>
-      <c r="D6" s="1">
+      <c r="G7" s="1">
         <v>46.470588235294123</v>
       </c>
-      <c r="E6" s="1">
+      <c r="H7" s="1">
         <v>35</v>
       </c>
-      <c r="F6" s="1">
+      <c r="I7" s="1">
         <v>28.393881453154876</v>
       </c>
-      <c r="G6" s="1">
+      <c r="J7" s="1">
         <v>25</v>
       </c>
-      <c r="H6" s="1">
+      <c r="K7" s="1">
         <v>23</v>
       </c>
-      <c r="I6" s="1">
+      <c r="L7" s="1">
         <v>21.510516252390055</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="M7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1">
         <f t="shared" si="0"/>
         <v>46.249920000000003</v>
       </c>
-      <c r="D7" s="1">
+      <c r="G8" s="1">
         <v>45.792000000000002</v>
       </c>
-      <c r="E7" s="1">
-        <f>D7-(D7*0.02)</f>
+      <c r="H8" s="1">
+        <f>G8-(G8*0.02)</f>
         <v>44.876159999999999</v>
       </c>
-      <c r="F7" s="1">
-        <f>E7-(E7*0.02)</f>
+      <c r="I8" s="1">
+        <f>H8-(H8*0.02)</f>
         <v>43.978636799999997</v>
       </c>
-      <c r="G7" s="1">
-        <f>F7-(F7*0.02)</f>
+      <c r="J8" s="1">
+        <f>I8-(I8*0.02)</f>
         <v>43.099064063999997</v>
       </c>
-      <c r="H7" s="1">
-        <f>G7-(G7*0.02)</f>
+      <c r="K8" s="1">
+        <f>J8-(J8*0.02)</f>
         <v>42.237082782719995</v>
       </c>
-      <c r="I7" s="1">
-        <f>H7+(H7*0.02)</f>
+      <c r="L8" s="1">
+        <f>K8+(K8*0.02)</f>
         <v>43.081824438374397</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="1">
-        <v>96.367112810707454</v>
-      </c>
-      <c r="D10" s="1">
-        <v>96.367112810707454</v>
-      </c>
+      <c r="M8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
